--- a/static/standards-correlations/Kentucky_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Kentucky_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$55</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Kentucky K-12 CS Standards, established October 2018</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Kentucky K-12 CS Standards, established October 2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -913,7 +914,7 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Ext 5.3G (Secret Messages / HTTPS) shows credentials exposed over HTTP. Discovery Systems 10 covers phishing as an attack on the person rather than the system.</t>
+          <t>Ext 5.3G (Secret Messages / HTTPS) shows credentials exposed over HTTP. Introductory Systems 10 covers phishing as an attack on the person rather than the system.</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1867,7 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Unit 5.3 teaches version control, repositories, and commits directly. Discovery Systems 13 and 14 assign team roles and manage a project timeline.</t>
+          <t>Unit 5.3 teaches version control, repositories, and commits directly. Introductory Systems 13 and 14 assign team roles and manage a project timeline.</t>
         </is>
       </c>
     </row>
@@ -2759,6 +2760,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -2803,7 +2805,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2817,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2915,6 +2917,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
@@ -2932,7 +2936,7 @@
 SOURCE NOTE: Standard codes and statements were transcribed from the CodeHS published Kentucky 9-12 standards framework. The October 2018 establishment date and graduation context were verified against KDE. Verify wording against the official KDE standards document before using this crosswalk in any formal submission.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.</t>
         </is>
       </c>
